--- a/data/modelling/clustering/tv/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/tv/df_brand_per_cluster.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,21 +479,31 @@
           <t>Hisense</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Kanji</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero buenos</t>
+          <t>Los de menor calidad</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -505,16 +515,22 @@
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -524,71 +540,126 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
         <v>9</v>
       </c>
-      <c r="F3" t="n">
-        <v>17</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>13</v>
-      </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero calidad acorde</t>
+          <t>Tradicionales</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
         <v>6</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Calidad a alto costo</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
-        <v>7</v>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/clustering/tv/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/tv/df_brand_per_cluster.xlsx
@@ -425,232 +425,316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Noblex</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RCA</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>BGH</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Hitachi</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>BGH</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>TCL</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Philco</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Kanji</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Candy</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>AOC</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Enova</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Hisense</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Hyundai</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Kanji</t>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Quint</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Kodak</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Los de menor calidad</t>
+          <t>Alta calidad a buen precio</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2" t="n">
         <v>7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Los numero 1</t>
+          <t>Barato pero calidad madia/baja</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="S3" t="n">
         <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Tradicionales</t>
+          <t>Calidad media/baja a precio medio</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
       </c>
       <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
         <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Calidad a alto costo</t>
+          <t>Alta calidad pero precio alto</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
-        <v>8</v>
-      </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -659,7 +743,25 @@
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/clustering/tv/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/tv/df_brand_per_cluster.xlsx
@@ -584,7 +584,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
       <c r="B3" t="n">

--- a/data/modelling/clustering/tv/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/tv/df_brand_per_cluster.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
